--- a/sheets/대금율보/검수/동백타령 중중모리.xlsx
+++ b/sheets/대금율보/검수/동백타령 중중모리.xlsx
@@ -2000,7 +2000,7 @@
       <c r="D4" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">林
-–‹
+–
 太</t>
         </is>
       </c>
@@ -2026,7 +2026,7 @@
       </c>
       <c r="D5" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 林
 –</t>
         </is>
@@ -2037,8 +2037,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">林
-‹</t>
+          <t xml:space="preserve">林</t>
         </is>
       </c>
       <c r="C6" s="24" t="inlineStr">
@@ -2145,8 +2144,7 @@
         <is>
           <t xml:space="preserve">汰
 南)
-林
-‹</t>
+林</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -2248,8 +2246,7 @@
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">太
-‹</t>
+          <t xml:space="preserve">太</t>
         </is>
       </c>
       <c r="C14" s="24" t="inlineStr">

--- a/sheets/대금율보/검수/동백타령 중중모리.xlsx
+++ b/sheets/대금율보/검수/동백타령 중중모리.xlsx
@@ -1938,16 +1938,16 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="13.46" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="13.46" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="90.91" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1958,7 +1958,7 @@
       <c r="D2" s="20"/>
       <c r="E2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="101.66" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -1983,7 +1983,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="101.66" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2010,7 +2010,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="101.66" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="E5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="101.66" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2058,7 +2058,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="101.66" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="101.66" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2112,7 +2112,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="101.66" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2138,7 +2138,7 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="101.66" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -2163,7 +2163,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="101.66" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2188,7 +2188,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="101.66" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2215,7 +2215,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="101.66" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2242,7 +2242,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="101.66" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="101.66" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2291,7 +2291,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="101.66" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="101.66" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="101.66" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2378,6 +2378,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="44"/>
 </worksheet>
 </file>